--- a/outputs/rtm-maintenance-final/第14小组_基于大模型的个人知识库系统_需求跟踪矩阵.xlsx
+++ b/outputs/rtm-maintenance-final/第14小组_基于大模型的个人知识库系统_需求跟踪矩阵.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cowork\wenkb\outputs\rtm-maintenance-final\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\111学习\4.1大四上\校内实习\wenkb-main\outputs\rtm-maintenance-final\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8964C0EE-27BB-414A-84CB-A011C5C88D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="9880" activeTab="2"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="需求跟踪矩阵封面" sheetId="1" r:id="rId1"/>
@@ -29,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="230">
   <si>
     <t>密级：</t>
   </si>
@@ -725,21 +724,21 @@
   </si>
   <si>
     <t>PD=需求与设计基线，COD=当前代码实现，UT=当前测试/验证证据。△ 不代表需求取消，而是表示仍有实现或接口级测试缺口。</t>
+  </si>
+  <si>
+    <t>吴剑光</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="0.0%"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="2">
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -845,7 +844,7 @@
     <font>
       <sz val="12"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
@@ -853,158 +852,24 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="43">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1071,194 +936,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="20">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1395,357 +1074,119 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+  </cellStyleXfs>
+  <cellXfs count="56">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="53">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="11" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1764,113 +1205,185 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="16" fillId="11" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -1881,7 +1394,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1909,161 +1422,47 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -2079,13 +1478,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="/xl/media/image.png"/>
+        <xdr:cNvPr id="2" name="/xl/media/image.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2117,13 +1522,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="/xl/media/image2.png"/>
+        <xdr:cNvPr id="3" name="/xl/media/image2.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2144,7 +1555,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -2160,13 +1571,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="/xl/media/image3.png"/>
+        <xdr:cNvPr id="2" name="/xl/media/image3.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2198,13 +1615,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="/xl/media/image4.png"/>
+        <xdr:cNvPr id="3" name="/xl/media/image4.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2225,7 +1648,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -2241,13 +1664,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="/xl/media/image5.png"/>
+        <xdr:cNvPr id="2" name="/xl/media/image5.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2279,13 +1708,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="/xl/media/image6.png"/>
+        <xdr:cNvPr id="3" name="/xl/media/image6.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2306,7 +1741,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -2322,13 +1757,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="/xl/media/image7.png"/>
+        <xdr:cNvPr id="2" name="/xl/media/image7.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2360,13 +1801,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="/xl/media/image8.png"/>
+        <xdr:cNvPr id="3" name="/xl/media/image8.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2596,1372 +2043,1400 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A3:H37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="8" width="13.8181818181818" customWidth="1"/>
+    <col min="1" max="8" width="13.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="25" customHeight="1" spans="1:8">
-      <c r="A3" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="35" t="s">
+    <row r="3" spans="1:8" ht="25.05" customHeight="1">
+      <c r="A3" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="24" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" ht="25" customHeight="1" spans="1:8">
-      <c r="H4" s="36" t="s">
+    <row r="4" spans="1:8" ht="25.05" customHeight="1">
+      <c r="H4" s="25" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" ht="25" customHeight="1" spans="1:8">
-      <c r="A5" s="37" t="s">
+    <row r="5" spans="1:8" ht="25.05" customHeight="1">
+      <c r="A5" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="38" t="s">
+      <c r="B5" s="33"/>
+      <c r="G5" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="39"/>
-    </row>
-    <row r="6" ht="10" customHeight="1"/>
-    <row r="7" ht="10" customHeight="1"/>
-    <row r="8" ht="10" customHeight="1"/>
-    <row r="9" ht="10" customHeight="1"/>
-    <row r="10" ht="10" customHeight="1"/>
-    <row r="11" ht="10" customHeight="1"/>
-    <row r="12" ht="10" customHeight="1"/>
-    <row r="13" ht="49.75" customHeight="1" spans="1:8">
-      <c r="A13" s="40" t="s">
+      <c r="H5" s="41"/>
+    </row>
+    <row r="6" spans="1:8" ht="10.050000000000001" customHeight="1"/>
+    <row r="7" spans="1:8" ht="10.050000000000001" customHeight="1"/>
+    <row r="8" spans="1:8" ht="10.050000000000001" customHeight="1"/>
+    <row r="9" spans="1:8" ht="10.050000000000001" customHeight="1"/>
+    <row r="10" spans="1:8" ht="10.050000000000001" customHeight="1"/>
+    <row r="11" spans="1:8" ht="10.050000000000001" customHeight="1"/>
+    <row r="12" spans="1:8" ht="10.050000000000001" customHeight="1"/>
+    <row r="13" spans="1:8" ht="49.8" customHeight="1">
+      <c r="A13" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="3"/>
-    </row>
-    <row r="14" ht="9" customHeight="1"/>
-    <row r="15" ht="39" customHeight="1" spans="1:8">
-      <c r="A15" s="42" t="s">
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="35"/>
+    </row>
+    <row r="14" spans="1:8" ht="9" customHeight="1"/>
+    <row r="15" spans="1:8" ht="39" customHeight="1">
+      <c r="A15" s="44" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="16" ht="10" customHeight="1"/>
-    <row r="17" ht="10" customHeight="1"/>
-    <row r="18" ht="10" customHeight="1"/>
-    <row r="19" ht="10" customHeight="1"/>
-    <row r="20" ht="25" customHeight="1" spans="1:5">
-      <c r="A20" s="43" t="s">
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+    </row>
+    <row r="16" spans="1:8" ht="10.050000000000001" customHeight="1"/>
+    <row r="17" spans="1:8" ht="10.050000000000001" customHeight="1"/>
+    <row r="18" spans="1:8" ht="10.050000000000001" customHeight="1"/>
+    <row r="19" spans="1:8" ht="10.050000000000001" customHeight="1"/>
+    <row r="20" spans="1:8" ht="25.05" customHeight="1">
+      <c r="A20" s="45" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" ht="10" customHeight="1"/>
-    <row r="22" ht="10" customHeight="1" spans="1:5">
-      <c r="A22" s="44"/>
-    </row>
-    <row r="23" ht="10" customHeight="1"/>
-    <row r="24" ht="10" customHeight="1" spans="1:5">
-      <c r="A24" s="44"/>
-    </row>
-    <row r="25" ht="10" customHeight="1"/>
-    <row r="26" ht="10" customHeight="1" spans="1:5">
-      <c r="A26" s="44"/>
-      <c r="E26" s="44"/>
-    </row>
-    <row r="27" ht="10" customHeight="1"/>
-    <row r="28" ht="10" customHeight="1"/>
-    <row r="29" ht="10" customHeight="1"/>
-    <row r="30" ht="10" customHeight="1"/>
-    <row r="31" ht="10" customHeight="1"/>
-    <row r="32" ht="10" customHeight="1"/>
-    <row r="33" ht="10" customHeight="1"/>
-    <row r="34" ht="10" customHeight="1"/>
-    <row r="35" ht="10" customHeight="1"/>
-    <row r="36" ht="25" customHeight="1" spans="1:8">
-      <c r="A36" s="45" t="s">
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+    </row>
+    <row r="21" spans="1:8" ht="10.050000000000001" customHeight="1"/>
+    <row r="22" spans="1:8" ht="10.050000000000001" customHeight="1">
+      <c r="A22" s="26"/>
+    </row>
+    <row r="23" spans="1:8" ht="10.050000000000001" customHeight="1"/>
+    <row r="24" spans="1:8" ht="10.050000000000001" customHeight="1">
+      <c r="A24" s="26"/>
+    </row>
+    <row r="25" spans="1:8" ht="10.050000000000001" customHeight="1"/>
+    <row r="26" spans="1:8" ht="10.050000000000001" customHeight="1">
+      <c r="A26" s="26"/>
+      <c r="E26" s="26"/>
+    </row>
+    <row r="27" spans="1:8" ht="10.050000000000001" customHeight="1"/>
+    <row r="28" spans="1:8" ht="10.050000000000001" customHeight="1"/>
+    <row r="29" spans="1:8" ht="10.050000000000001" customHeight="1"/>
+    <row r="30" spans="1:8" ht="10.050000000000001" customHeight="1"/>
+    <row r="31" spans="1:8" ht="10.050000000000001" customHeight="1"/>
+    <row r="32" spans="1:8" ht="10.050000000000001" customHeight="1"/>
+    <row r="33" spans="1:8" ht="10.050000000000001" customHeight="1"/>
+    <row r="34" spans="1:8" ht="10.050000000000001" customHeight="1"/>
+    <row r="35" spans="1:8" ht="10.050000000000001" customHeight="1"/>
+    <row r="36" spans="1:8" ht="25.05" customHeight="1">
+      <c r="A36" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="B36" s="46">
+      <c r="B36" s="28">
         <v>7</v>
       </c>
-      <c r="C36" s="45" t="s">
+      <c r="C36" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="D36" s="46">
+      <c r="D36" s="28">
         <v>2</v>
       </c>
-      <c r="E36" s="45" t="s">
+      <c r="E36" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="F36" s="47">
+      <c r="F36" s="29">
         <v>4</v>
       </c>
-      <c r="G36" s="45" t="s">
+      <c r="G36" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="H36" s="48">
+      <c r="H36" s="30">
         <v>46269</v>
       </c>
     </row>
-    <row r="37" ht="25" customHeight="1" spans="1:8">
-      <c r="A37" s="49" t="s">
+    <row r="37" spans="1:8" ht="25.05" customHeight="1">
+      <c r="A37" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="B37" s="47" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="50"/>
-      <c r="D37" s="51"/>
-      <c r="E37" s="49" t="s">
+      <c r="B37" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="47"/>
+      <c r="D37" s="48"/>
+      <c r="E37" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="F37" s="52" t="s">
-        <v>13</v>
-      </c>
-      <c r="G37" s="50"/>
-      <c r="H37" s="51"/>
+      <c r="F37" s="55" t="s">
+        <v>229</v>
+      </c>
+      <c r="G37" s="47"/>
+      <c r="H37" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F37:H37"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A20:H20"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F37:H37"/>
   </mergeCells>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:P27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="2.63636363636364" customWidth="1"/>
-    <col min="2" max="2" width="7.63636363636364" customWidth="1"/>
-    <col min="3" max="3" width="12.6363636363636" customWidth="1"/>
-    <col min="4" max="4" width="66.6363636363636" customWidth="1"/>
-    <col min="5" max="5" width="30.6363636363636" customWidth="1"/>
-    <col min="6" max="7" width="12.6363636363636" customWidth="1"/>
-    <col min="8" max="12" width="10.6363636363636" customWidth="1"/>
-    <col min="13" max="14" width="12.6363636363636" customWidth="1"/>
-    <col min="15" max="16" width="14.6363636363636" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="66.6640625" customWidth="1"/>
+    <col min="5" max="5" width="30.6640625" customWidth="1"/>
+    <col min="6" max="7" width="12.6640625" customWidth="1"/>
+    <col min="8" max="12" width="10.6640625" customWidth="1"/>
+    <col min="13" max="14" width="12.6640625" customWidth="1"/>
+    <col min="15" max="16" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="2:16">
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="2:16" ht="21" customHeight="1">
+      <c r="B1" s="32" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" ht="31.25" customHeight="1" spans="2:16">
-      <c r="B2" s="10" t="s">
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+    </row>
+    <row r="2" spans="2:16" ht="31.2" customHeight="1">
+      <c r="B2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" s="10" t="s">
+      <c r="K2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="N2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="P2" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" ht="54" customHeight="1" spans="2:16">
-      <c r="B3" s="19">
+    <row r="3" spans="2:16" ht="54" customHeight="1">
+      <c r="B3" s="14">
         <v>1</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="15">
         <v>46267</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="19">
-        <v>0</v>
-      </c>
-      <c r="I3" s="19">
-        <v>25</v>
-      </c>
-      <c r="J3" s="19">
-        <v>0</v>
-      </c>
-      <c r="K3" s="19">
-        <v>0</v>
-      </c>
-      <c r="L3" s="19">
-        <v>25</v>
-      </c>
-      <c r="M3" s="22">
-        <v>0</v>
-      </c>
-      <c r="N3" s="19" t="s">
+      <c r="H3" s="14">
+        <v>0</v>
+      </c>
+      <c r="I3" s="14">
+        <v>25</v>
+      </c>
+      <c r="J3" s="14">
+        <v>0</v>
+      </c>
+      <c r="K3" s="14">
+        <v>0</v>
+      </c>
+      <c r="L3" s="14">
+        <v>25</v>
+      </c>
+      <c r="M3" s="17">
+        <v>0</v>
+      </c>
+      <c r="N3" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="O3" s="19" t="s">
+      <c r="O3" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="P3" s="19" t="s">
+      <c r="P3" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" ht="54" customHeight="1" spans="2:16">
-      <c r="B4" s="19">
+    <row r="4" spans="2:16" ht="54" customHeight="1">
+      <c r="B4" s="14">
         <v>2</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="15">
         <v>46267</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="19">
-        <v>25</v>
-      </c>
-      <c r="I4" s="19">
-        <v>0</v>
-      </c>
-      <c r="J4" s="19">
-        <v>0</v>
-      </c>
-      <c r="K4" s="19">
-        <v>0</v>
-      </c>
-      <c r="L4" s="19">
-        <v>25</v>
-      </c>
-      <c r="M4" s="22">
-        <v>0</v>
-      </c>
-      <c r="N4" s="19" t="s">
+      <c r="H4" s="14">
+        <v>25</v>
+      </c>
+      <c r="I4" s="14">
+        <v>0</v>
+      </c>
+      <c r="J4" s="14">
+        <v>0</v>
+      </c>
+      <c r="K4" s="14">
+        <v>0</v>
+      </c>
+      <c r="L4" s="14">
+        <v>25</v>
+      </c>
+      <c r="M4" s="17">
+        <v>0</v>
+      </c>
+      <c r="N4" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="O4" s="19" t="s">
+      <c r="O4" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="P4" s="19" t="s">
+      <c r="P4" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" ht="54" customHeight="1" spans="2:16">
-      <c r="B5" s="19">
+    <row r="5" spans="2:16" ht="54" customHeight="1">
+      <c r="B5" s="14">
         <v>3</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="15">
         <v>46267</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="19">
-        <v>25</v>
-      </c>
-      <c r="I5" s="19">
-        <v>0</v>
-      </c>
-      <c r="J5" s="19">
-        <v>0</v>
-      </c>
-      <c r="K5" s="19">
-        <v>0</v>
-      </c>
-      <c r="L5" s="19">
-        <v>25</v>
-      </c>
-      <c r="M5" s="22">
-        <v>0</v>
-      </c>
-      <c r="N5" s="19" t="s">
+      <c r="H5" s="14">
+        <v>25</v>
+      </c>
+      <c r="I5" s="14">
+        <v>0</v>
+      </c>
+      <c r="J5" s="14">
+        <v>0</v>
+      </c>
+      <c r="K5" s="14">
+        <v>0</v>
+      </c>
+      <c r="L5" s="14">
+        <v>25</v>
+      </c>
+      <c r="M5" s="17">
+        <v>0</v>
+      </c>
+      <c r="N5" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="O5" s="19" t="s">
+      <c r="O5" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="P5" s="19" t="s">
+      <c r="P5" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6" ht="54" customHeight="1" spans="2:16">
-      <c r="B6" s="19">
+    <row r="6" spans="2:16" ht="54" customHeight="1">
+      <c r="B6" s="14">
         <v>4</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="15">
         <v>46267</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="19">
-        <v>25</v>
-      </c>
-      <c r="I6" s="19">
-        <v>0</v>
-      </c>
-      <c r="J6" s="19">
-        <v>0</v>
-      </c>
-      <c r="K6" s="19">
-        <v>0</v>
-      </c>
-      <c r="L6" s="19">
-        <v>25</v>
-      </c>
-      <c r="M6" s="22">
-        <v>0</v>
-      </c>
-      <c r="N6" s="19" t="s">
+      <c r="H6" s="14">
+        <v>25</v>
+      </c>
+      <c r="I6" s="14">
+        <v>0</v>
+      </c>
+      <c r="J6" s="14">
+        <v>0</v>
+      </c>
+      <c r="K6" s="14">
+        <v>0</v>
+      </c>
+      <c r="L6" s="14">
+        <v>25</v>
+      </c>
+      <c r="M6" s="17">
+        <v>0</v>
+      </c>
+      <c r="N6" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="O6" s="19" t="s">
+      <c r="O6" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="P6" s="19" t="s">
+      <c r="P6" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="7" ht="54" customHeight="1" spans="2:16">
-      <c r="B7" s="19">
+    <row r="7" spans="2:16" ht="54" customHeight="1">
+      <c r="B7" s="14">
         <v>5</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="15">
         <v>46267</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="19">
-        <v>25</v>
-      </c>
-      <c r="I7" s="19">
-        <v>0</v>
-      </c>
-      <c r="J7" s="19">
-        <v>0</v>
-      </c>
-      <c r="K7" s="19">
-        <v>0</v>
-      </c>
-      <c r="L7" s="19">
-        <v>25</v>
-      </c>
-      <c r="M7" s="22">
-        <v>0</v>
-      </c>
-      <c r="N7" s="19" t="s">
+      <c r="H7" s="14">
+        <v>25</v>
+      </c>
+      <c r="I7" s="14">
+        <v>0</v>
+      </c>
+      <c r="J7" s="14">
+        <v>0</v>
+      </c>
+      <c r="K7" s="14">
+        <v>0</v>
+      </c>
+      <c r="L7" s="14">
+        <v>25</v>
+      </c>
+      <c r="M7" s="17">
+        <v>0</v>
+      </c>
+      <c r="N7" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="O7" s="19" t="s">
+      <c r="O7" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="P7" s="19" t="s">
+      <c r="P7" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" ht="54" customHeight="1" spans="2:16">
-      <c r="B8" s="19">
+    <row r="8" spans="2:16" ht="54" customHeight="1">
+      <c r="B8" s="14">
         <v>6</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="15">
         <v>46267</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="H8" s="19">
-        <v>25</v>
-      </c>
-      <c r="I8" s="19">
-        <v>0</v>
-      </c>
-      <c r="J8" s="19">
-        <v>0</v>
-      </c>
-      <c r="K8" s="19">
+      <c r="H8" s="14">
+        <v>25</v>
+      </c>
+      <c r="I8" s="14">
+        <v>0</v>
+      </c>
+      <c r="J8" s="14">
+        <v>0</v>
+      </c>
+      <c r="K8" s="14">
         <v>1</v>
       </c>
-      <c r="L8" s="19">
-        <v>25</v>
-      </c>
-      <c r="M8" s="22">
+      <c r="L8" s="14">
+        <v>25</v>
+      </c>
+      <c r="M8" s="17">
         <v>0.04</v>
       </c>
-      <c r="N8" s="19" t="s">
+      <c r="N8" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="O8" s="19" t="s">
+      <c r="O8" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="P8" s="19" t="s">
+      <c r="P8" s="14" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="9" ht="54" customHeight="1" spans="2:16">
-      <c r="B9" s="19">
+    <row r="9" spans="2:16" ht="54" customHeight="1">
+      <c r="B9" s="14">
         <v>7</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="15">
         <v>46268</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="19">
-        <v>25</v>
-      </c>
-      <c r="I9" s="19">
-        <v>0</v>
-      </c>
-      <c r="J9" s="19">
-        <v>0</v>
-      </c>
-      <c r="K9" s="19">
+      <c r="H9" s="14">
+        <v>25</v>
+      </c>
+      <c r="I9" s="14">
+        <v>0</v>
+      </c>
+      <c r="J9" s="14">
+        <v>0</v>
+      </c>
+      <c r="K9" s="14">
         <v>7</v>
       </c>
-      <c r="L9" s="19">
-        <v>25</v>
-      </c>
-      <c r="M9" s="22">
-        <v>0.28</v>
-      </c>
-      <c r="N9" s="19" t="s">
+      <c r="L9" s="14">
+        <v>25</v>
+      </c>
+      <c r="M9" s="17">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="N9" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="O9" s="19" t="s">
+      <c r="O9" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="P9" s="19" t="s">
+      <c r="P9" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="10" ht="54" customHeight="1" spans="2:16">
-      <c r="B10" s="19">
+    <row r="10" spans="2:16" ht="54" customHeight="1">
+      <c r="B10" s="14">
         <v>8</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="15">
         <v>46268</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" s="19">
-        <v>25</v>
-      </c>
-      <c r="I10" s="19">
-        <v>0</v>
-      </c>
-      <c r="J10" s="19">
-        <v>0</v>
-      </c>
-      <c r="K10" s="19">
+      <c r="G10" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="14">
+        <v>25</v>
+      </c>
+      <c r="I10" s="14">
+        <v>0</v>
+      </c>
+      <c r="J10" s="14">
+        <v>0</v>
+      </c>
+      <c r="K10" s="14">
         <v>1</v>
       </c>
-      <c r="L10" s="19">
-        <v>25</v>
-      </c>
-      <c r="M10" s="22">
+      <c r="L10" s="14">
+        <v>25</v>
+      </c>
+      <c r="M10" s="17">
         <v>0.04</v>
       </c>
-      <c r="N10" s="19" t="s">
+      <c r="N10" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="O10" s="19" t="s">
+      <c r="O10" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="P10" s="19" t="s">
+      <c r="P10" s="14" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="11" ht="54" customHeight="1" spans="2:16">
-      <c r="B11" s="19">
+    <row r="11" spans="2:16" ht="54" customHeight="1">
+      <c r="B11" s="14">
         <v>9</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="15">
         <v>46268</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="19">
-        <v>25</v>
-      </c>
-      <c r="I11" s="19">
-        <v>0</v>
-      </c>
-      <c r="J11" s="19">
-        <v>0</v>
-      </c>
-      <c r="K11" s="19">
+      <c r="H11" s="14">
+        <v>25</v>
+      </c>
+      <c r="I11" s="14">
+        <v>0</v>
+      </c>
+      <c r="J11" s="14">
+        <v>0</v>
+      </c>
+      <c r="K11" s="14">
         <v>7</v>
       </c>
-      <c r="L11" s="19">
-        <v>25</v>
-      </c>
-      <c r="M11" s="22">
-        <v>0.28</v>
-      </c>
-      <c r="N11" s="19" t="s">
+      <c r="L11" s="14">
+        <v>25</v>
+      </c>
+      <c r="M11" s="17">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="N11" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="O11" s="19" t="s">
+      <c r="O11" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="P11" s="19" t="s">
+      <c r="P11" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="12" ht="54" customHeight="1" spans="2:16">
-      <c r="B12" s="19">
+    <row r="12" spans="2:16" ht="54" customHeight="1">
+      <c r="B12" s="14">
         <v>10</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="15">
         <v>46268</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="H12" s="19">
-        <v>25</v>
-      </c>
-      <c r="I12" s="19">
-        <v>0</v>
-      </c>
-      <c r="J12" s="19">
-        <v>0</v>
-      </c>
-      <c r="K12" s="19">
+      <c r="H12" s="14">
+        <v>25</v>
+      </c>
+      <c r="I12" s="14">
+        <v>0</v>
+      </c>
+      <c r="J12" s="14">
+        <v>0</v>
+      </c>
+      <c r="K12" s="14">
         <v>1</v>
       </c>
-      <c r="L12" s="19">
-        <v>25</v>
-      </c>
-      <c r="M12" s="22">
+      <c r="L12" s="14">
+        <v>25</v>
+      </c>
+      <c r="M12" s="17">
         <v>0.04</v>
       </c>
-      <c r="N12" s="19" t="s">
+      <c r="N12" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="O12" s="19" t="s">
+      <c r="O12" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="P12" s="19" t="s">
+      <c r="P12" s="14" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="13" ht="54" customHeight="1" spans="2:16">
-      <c r="B13" s="19">
+    <row r="13" spans="2:16" ht="54" customHeight="1">
+      <c r="B13" s="14">
         <v>11</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="15">
         <v>46268</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="D13" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="H13" s="19">
-        <v>25</v>
-      </c>
-      <c r="I13" s="19">
-        <v>0</v>
-      </c>
-      <c r="J13" s="19">
-        <v>0</v>
-      </c>
-      <c r="K13" s="19">
+      <c r="H13" s="14">
+        <v>25</v>
+      </c>
+      <c r="I13" s="14">
+        <v>0</v>
+      </c>
+      <c r="J13" s="14">
+        <v>0</v>
+      </c>
+      <c r="K13" s="14">
         <v>4</v>
       </c>
-      <c r="L13" s="19">
-        <v>25</v>
-      </c>
-      <c r="M13" s="22">
+      <c r="L13" s="14">
+        <v>25</v>
+      </c>
+      <c r="M13" s="17">
         <v>0.16</v>
       </c>
-      <c r="N13" s="19" t="s">
+      <c r="N13" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="O13" s="19" t="s">
+      <c r="O13" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="P13" s="19" t="s">
+      <c r="P13" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="14" ht="54" customHeight="1" spans="2:16">
-      <c r="B14" s="19">
+    <row r="14" spans="2:16" ht="54" customHeight="1">
+      <c r="B14" s="14">
         <v>12</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="15">
         <v>46268</v>
       </c>
-      <c r="D14" s="21" t="s">
+      <c r="D14" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="H14" s="19">
-        <v>25</v>
-      </c>
-      <c r="I14" s="19">
-        <v>0</v>
-      </c>
-      <c r="J14" s="19">
-        <v>0</v>
-      </c>
-      <c r="K14" s="19">
+      <c r="H14" s="14">
+        <v>25</v>
+      </c>
+      <c r="I14" s="14">
+        <v>0</v>
+      </c>
+      <c r="J14" s="14">
+        <v>0</v>
+      </c>
+      <c r="K14" s="14">
         <v>5</v>
       </c>
-      <c r="L14" s="19">
-        <v>25</v>
-      </c>
-      <c r="M14" s="22">
+      <c r="L14" s="14">
+        <v>25</v>
+      </c>
+      <c r="M14" s="17">
         <v>0.2</v>
       </c>
-      <c r="N14" s="19" t="s">
+      <c r="N14" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="O14" s="19" t="s">
+      <c r="O14" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="P14" s="19" t="s">
+      <c r="P14" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="15" ht="54" customHeight="1" spans="2:16">
-      <c r="B15" s="19">
-        <v>13</v>
-      </c>
-      <c r="C15" s="20">
+    <row r="15" spans="2:16" ht="54" customHeight="1">
+      <c r="B15" s="14">
+        <v>13</v>
+      </c>
+      <c r="C15" s="15">
         <v>46268</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="F15" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="19" t="s">
+      <c r="G15" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="H15" s="19">
-        <v>25</v>
-      </c>
-      <c r="I15" s="19">
-        <v>0</v>
-      </c>
-      <c r="J15" s="19">
-        <v>0</v>
-      </c>
-      <c r="K15" s="19">
+      <c r="H15" s="14">
+        <v>25</v>
+      </c>
+      <c r="I15" s="14">
+        <v>0</v>
+      </c>
+      <c r="J15" s="14">
+        <v>0</v>
+      </c>
+      <c r="K15" s="14">
         <v>1</v>
       </c>
-      <c r="L15" s="19">
-        <v>25</v>
-      </c>
-      <c r="M15" s="22">
+      <c r="L15" s="14">
+        <v>25</v>
+      </c>
+      <c r="M15" s="17">
         <v>0.04</v>
       </c>
-      <c r="N15" s="19" t="s">
+      <c r="N15" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="O15" s="19" t="s">
+      <c r="O15" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="P15" s="19" t="s">
+      <c r="P15" s="14" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="16" ht="54" customHeight="1" spans="2:16">
-      <c r="B16" s="19">
+    <row r="16" spans="2:16" ht="54" customHeight="1">
+      <c r="B16" s="14">
         <v>14</v>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="15">
         <v>46268</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="H16" s="19">
-        <v>25</v>
-      </c>
-      <c r="I16" s="19">
-        <v>0</v>
-      </c>
-      <c r="J16" s="19">
-        <v>0</v>
-      </c>
-      <c r="K16" s="19">
+      <c r="H16" s="14">
+        <v>25</v>
+      </c>
+      <c r="I16" s="14">
+        <v>0</v>
+      </c>
+      <c r="J16" s="14">
+        <v>0</v>
+      </c>
+      <c r="K16" s="14">
         <v>9</v>
       </c>
-      <c r="L16" s="19">
-        <v>25</v>
-      </c>
-      <c r="M16" s="22">
+      <c r="L16" s="14">
+        <v>25</v>
+      </c>
+      <c r="M16" s="17">
         <v>0.36</v>
       </c>
-      <c r="N16" s="19" t="s">
+      <c r="N16" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="O16" s="19" t="s">
+      <c r="O16" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="P16" s="19" t="s">
+      <c r="P16" s="14" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="17" ht="54" customHeight="1" spans="2:16">
-      <c r="B17" s="19">
+    <row r="17" spans="2:16" ht="54" customHeight="1">
+      <c r="B17" s="14">
         <v>15</v>
       </c>
-      <c r="C17" s="20">
+      <c r="C17" s="15">
         <v>46268</v>
       </c>
-      <c r="D17" s="21" t="s">
+      <c r="D17" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F17" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G17" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17" s="19">
-        <v>25</v>
-      </c>
-      <c r="I17" s="19">
-        <v>0</v>
-      </c>
-      <c r="J17" s="19">
-        <v>0</v>
-      </c>
-      <c r="K17" s="19">
+      <c r="G17" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="14">
+        <v>25</v>
+      </c>
+      <c r="I17" s="14">
+        <v>0</v>
+      </c>
+      <c r="J17" s="14">
+        <v>0</v>
+      </c>
+      <c r="K17" s="14">
         <v>2</v>
       </c>
-      <c r="L17" s="19">
-        <v>25</v>
-      </c>
-      <c r="M17" s="22">
+      <c r="L17" s="14">
+        <v>25</v>
+      </c>
+      <c r="M17" s="17">
         <v>0.08</v>
       </c>
-      <c r="N17" s="19" t="s">
+      <c r="N17" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="O17" s="19" t="s">
+      <c r="O17" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="P17" s="19" t="s">
+      <c r="P17" s="14" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="18" ht="54" customHeight="1" spans="2:16">
-      <c r="B18" s="19">
+    <row r="18" spans="2:16" ht="54" customHeight="1">
+      <c r="B18" s="14">
         <v>16</v>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="15">
         <v>46268</v>
       </c>
-      <c r="D18" s="21" t="s">
+      <c r="D18" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="F18" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G18" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="H18" s="19">
-        <v>25</v>
-      </c>
-      <c r="I18" s="19">
-        <v>0</v>
-      </c>
-      <c r="J18" s="19">
-        <v>0</v>
-      </c>
-      <c r="K18" s="19">
+      <c r="G18" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="14">
+        <v>25</v>
+      </c>
+      <c r="I18" s="14">
+        <v>0</v>
+      </c>
+      <c r="J18" s="14">
+        <v>0</v>
+      </c>
+      <c r="K18" s="14">
         <v>6</v>
       </c>
-      <c r="L18" s="19">
-        <v>25</v>
-      </c>
-      <c r="M18" s="22">
+      <c r="L18" s="14">
+        <v>25</v>
+      </c>
+      <c r="M18" s="17">
         <v>0.24</v>
       </c>
-      <c r="N18" s="19" t="s">
+      <c r="N18" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="O18" s="19" t="s">
+      <c r="O18" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="P18" s="19" t="s">
+      <c r="P18" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="19" ht="54" customHeight="1" spans="2:16">
-      <c r="B19" s="19">
+    <row r="19" spans="2:16" ht="54" customHeight="1">
+      <c r="B19" s="14">
         <v>17</v>
       </c>
-      <c r="C19" s="20">
+      <c r="C19" s="15">
         <v>46268</v>
       </c>
-      <c r="D19" s="21" t="s">
+      <c r="D19" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="E19" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="F19" s="19" t="s">
+      <c r="F19" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G19" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="H19" s="19">
-        <v>25</v>
-      </c>
-      <c r="I19" s="19">
-        <v>0</v>
-      </c>
-      <c r="J19" s="19">
-        <v>0</v>
-      </c>
-      <c r="K19" s="19">
+      <c r="G19" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="14">
+        <v>25</v>
+      </c>
+      <c r="I19" s="14">
+        <v>0</v>
+      </c>
+      <c r="J19" s="14">
+        <v>0</v>
+      </c>
+      <c r="K19" s="14">
         <v>5</v>
       </c>
-      <c r="L19" s="19">
-        <v>25</v>
-      </c>
-      <c r="M19" s="22">
+      <c r="L19" s="14">
+        <v>25</v>
+      </c>
+      <c r="M19" s="17">
         <v>0.2</v>
       </c>
-      <c r="N19" s="19" t="s">
+      <c r="N19" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="O19" s="19" t="s">
+      <c r="O19" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="P19" s="19" t="s">
+      <c r="P19" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="20" ht="54" customHeight="1" spans="2:16">
-      <c r="B20" s="19">
+    <row r="20" spans="2:16" ht="54" customHeight="1">
+      <c r="B20" s="14">
         <v>18</v>
       </c>
-      <c r="C20" s="20">
+      <c r="C20" s="15">
         <v>46268</v>
       </c>
-      <c r="D20" s="21" t="s">
+      <c r="D20" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="F20" s="19" t="s">
+      <c r="F20" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G20" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="H20" s="19">
-        <v>25</v>
-      </c>
-      <c r="I20" s="19">
-        <v>0</v>
-      </c>
-      <c r="J20" s="19">
-        <v>0</v>
-      </c>
-      <c r="K20" s="19">
+      <c r="G20" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="14">
+        <v>25</v>
+      </c>
+      <c r="I20" s="14">
+        <v>0</v>
+      </c>
+      <c r="J20" s="14">
+        <v>0</v>
+      </c>
+      <c r="K20" s="14">
         <v>5</v>
       </c>
-      <c r="L20" s="19">
-        <v>25</v>
-      </c>
-      <c r="M20" s="22">
+      <c r="L20" s="14">
+        <v>25</v>
+      </c>
+      <c r="M20" s="17">
         <v>0.2</v>
       </c>
-      <c r="N20" s="19" t="s">
+      <c r="N20" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="O20" s="19" t="s">
+      <c r="O20" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="P20" s="19" t="s">
+      <c r="P20" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="21" ht="54" customHeight="1" spans="2:16">
-      <c r="B21" s="19">
+    <row r="21" spans="2:16" ht="54" customHeight="1">
+      <c r="B21" s="14">
         <v>19</v>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="15">
         <v>46268</v>
       </c>
-      <c r="D21" s="21" t="s">
+      <c r="D21" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="E21" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="F21" s="19" t="s">
+      <c r="F21" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="G21" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="H21" s="19">
-        <v>25</v>
-      </c>
-      <c r="I21" s="19">
-        <v>0</v>
-      </c>
-      <c r="J21" s="19">
-        <v>0</v>
-      </c>
-      <c r="K21" s="19">
+      <c r="G21" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="14">
+        <v>25</v>
+      </c>
+      <c r="I21" s="14">
+        <v>0</v>
+      </c>
+      <c r="J21" s="14">
+        <v>0</v>
+      </c>
+      <c r="K21" s="14">
         <v>4</v>
       </c>
-      <c r="L21" s="19">
-        <v>25</v>
-      </c>
-      <c r="M21" s="22">
+      <c r="L21" s="14">
+        <v>25</v>
+      </c>
+      <c r="M21" s="17">
         <v>0.16</v>
       </c>
-      <c r="N21" s="19" t="s">
+      <c r="N21" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="O21" s="19" t="s">
+      <c r="O21" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="P21" s="19" t="s">
+      <c r="P21" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="22" ht="54" customHeight="1" spans="2:16">
-      <c r="B22" s="19">
+    <row r="22" spans="2:16" ht="54" customHeight="1">
+      <c r="B22" s="14">
         <v>20</v>
       </c>
-      <c r="C22" s="20">
+      <c r="C22" s="15">
         <v>46269</v>
       </c>
-      <c r="D22" s="21" t="s">
+      <c r="D22" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="E22" s="19" t="s">
+      <c r="E22" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="F22" s="19" t="s">
+      <c r="F22" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="G22" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="H22" s="19">
-        <v>25</v>
-      </c>
-      <c r="I22" s="19">
-        <v>0</v>
-      </c>
-      <c r="J22" s="19">
-        <v>0</v>
-      </c>
-      <c r="K22" s="19">
+      <c r="G22" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="14">
+        <v>25</v>
+      </c>
+      <c r="I22" s="14">
+        <v>0</v>
+      </c>
+      <c r="J22" s="14">
+        <v>0</v>
+      </c>
+      <c r="K22" s="14">
         <v>1</v>
       </c>
-      <c r="L22" s="19">
-        <v>25</v>
-      </c>
-      <c r="M22" s="22">
+      <c r="L22" s="14">
+        <v>25</v>
+      </c>
+      <c r="M22" s="17">
         <v>0.04</v>
       </c>
-      <c r="N22" s="19" t="s">
+      <c r="N22" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="O22" s="19" t="s">
+      <c r="O22" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="P22" s="19" t="s">
+      <c r="P22" s="14" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="23" ht="72" customHeight="1" spans="2:16">
-      <c r="B23" s="19">
+    <row r="23" spans="2:16" ht="72" customHeight="1">
+      <c r="B23" s="14">
         <v>21</v>
       </c>
-      <c r="C23" s="20">
+      <c r="C23" s="15">
         <v>46271</v>
       </c>
-      <c r="D23" s="21" t="s">
+      <c r="D23" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="E23" s="19" t="s">
+      <c r="E23" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="F23" s="19" t="s">
+      <c r="F23" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G23" s="19" t="s">
+      <c r="G23" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="H23" s="19">
-        <v>25</v>
-      </c>
-      <c r="I23" s="19">
-        <v>0</v>
-      </c>
-      <c r="J23" s="19">
-        <v>0</v>
-      </c>
-      <c r="K23" s="19">
+      <c r="H23" s="14">
+        <v>25</v>
+      </c>
+      <c r="I23" s="14">
+        <v>0</v>
+      </c>
+      <c r="J23" s="14">
+        <v>0</v>
+      </c>
+      <c r="K23" s="14">
         <v>15</v>
       </c>
-      <c r="L23" s="19">
-        <v>25</v>
-      </c>
-      <c r="M23" s="22">
+      <c r="L23" s="14">
+        <v>25</v>
+      </c>
+      <c r="M23" s="17">
         <v>0.6</v>
       </c>
-      <c r="N23" s="19" t="s">
+      <c r="N23" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="O23" s="19" t="s">
+      <c r="O23" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="P23" s="19" t="s">
+      <c r="P23" s="14" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="24" ht="72" customHeight="1" spans="2:16">
-      <c r="B24" s="19">
+    <row r="24" spans="2:16" ht="72" customHeight="1">
+      <c r="B24" s="14">
         <v>22</v>
       </c>
-      <c r="C24" s="20">
+      <c r="C24" s="15">
         <v>46271</v>
       </c>
-      <c r="D24" s="21" t="s">
+      <c r="D24" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E24" s="19" t="s">
+      <c r="E24" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="F24" s="19" t="s">
+      <c r="F24" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G24" s="19" t="s">
+      <c r="G24" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="H24" s="19">
-        <v>25</v>
-      </c>
-      <c r="I24" s="19">
-        <v>0</v>
-      </c>
-      <c r="J24" s="19">
-        <v>0</v>
-      </c>
-      <c r="K24" s="19">
+      <c r="H24" s="14">
+        <v>25</v>
+      </c>
+      <c r="I24" s="14">
+        <v>0</v>
+      </c>
+      <c r="J24" s="14">
+        <v>0</v>
+      </c>
+      <c r="K24" s="14">
         <v>1</v>
       </c>
-      <c r="L24" s="19">
-        <v>25</v>
-      </c>
-      <c r="M24" s="22">
+      <c r="L24" s="14">
+        <v>25</v>
+      </c>
+      <c r="M24" s="17">
         <v>0.04</v>
       </c>
-      <c r="N24" s="19" t="s">
+      <c r="N24" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="O24" s="19" t="s">
+      <c r="O24" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="P24" s="19" t="s">
+      <c r="P24" s="14" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="25" ht="88" customHeight="1" spans="2:16">
-      <c r="B25" s="23">
+    <row r="25" spans="2:16" ht="88.05" customHeight="1">
+      <c r="B25" s="18">
         <v>23</v>
       </c>
-      <c r="C25" s="24">
+      <c r="C25" s="19">
         <v>46278</v>
       </c>
-      <c r="D25" s="25" t="s">
+      <c r="D25" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="E25" s="23" t="s">
+      <c r="E25" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="F25" s="23" t="s">
+      <c r="F25" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="G25" s="23" t="s">
+      <c r="G25" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="H25" s="23">
-        <v>25</v>
-      </c>
-      <c r="I25" s="23">
-        <v>0</v>
-      </c>
-      <c r="J25" s="23">
-        <v>0</v>
-      </c>
-      <c r="K25" s="23">
+      <c r="H25" s="18">
+        <v>25</v>
+      </c>
+      <c r="I25" s="18">
+        <v>0</v>
+      </c>
+      <c r="J25" s="18">
+        <v>0</v>
+      </c>
+      <c r="K25" s="18">
         <v>7</v>
       </c>
-      <c r="L25" s="23">
-        <v>25</v>
-      </c>
-      <c r="M25" s="26">
-        <v>0.28</v>
-      </c>
-      <c r="N25" s="23" t="s">
+      <c r="L25" s="18">
+        <v>25</v>
+      </c>
+      <c r="M25" s="21">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="N25" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="O25" s="23" t="s">
+      <c r="O25" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="P25" s="23" t="s">
+      <c r="P25" s="18" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="26" ht="66" customHeight="1" spans="2:16">
-      <c r="B26" s="23">
+    <row r="26" spans="2:16" ht="66" customHeight="1">
+      <c r="B26" s="18">
         <v>24</v>
       </c>
-      <c r="C26" s="24">
+      <c r="C26" s="19">
         <v>46279</v>
       </c>
-      <c r="D26" s="25" t="s">
+      <c r="D26" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="E26" s="23" t="s">
+      <c r="E26" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="F26" s="23" t="s">
+      <c r="F26" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="G26" s="23" t="s">
+      <c r="G26" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="H26" s="23">
-        <v>25</v>
-      </c>
-      <c r="I26" s="23">
-        <v>0</v>
-      </c>
-      <c r="J26" s="23">
-        <v>0</v>
-      </c>
-      <c r="K26" s="23">
+      <c r="H26" s="18">
+        <v>25</v>
+      </c>
+      <c r="I26" s="18">
+        <v>0</v>
+      </c>
+      <c r="J26" s="18">
+        <v>0</v>
+      </c>
+      <c r="K26" s="18">
         <v>1</v>
       </c>
-      <c r="L26" s="23">
-        <v>25</v>
-      </c>
-      <c r="M26" s="26">
+      <c r="L26" s="18">
+        <v>25</v>
+      </c>
+      <c r="M26" s="21">
         <v>0.04</v>
       </c>
-      <c r="N26" s="23" t="s">
+      <c r="N26" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="O26" s="23" t="s">
+      <c r="O26" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="P26" s="23" t="s">
+      <c r="P26" s="18" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="27" ht="42" customHeight="1" spans="2:16">
-      <c r="B27" s="27" t="s">
+    <row r="27" spans="2:16" ht="42" customHeight="1">
+      <c r="B27" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="29"/>
-      <c r="L27" s="30">
-        <v>25</v>
-      </c>
-      <c r="M27" s="30">
+      <c r="C27" s="50"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="51"/>
+      <c r="L27" s="22">
+        <v>25</v>
+      </c>
+      <c r="M27" s="22">
         <f>SUM(M3:M26)</f>
         <v>3.32</v>
       </c>
-      <c r="N27" s="31" t="s">
+      <c r="N27" s="52" t="s">
         <v>85</v>
       </c>
-      <c r="O27" s="32"/>
-      <c r="P27" s="33"/>
+      <c r="O27" s="53"/>
+      <c r="P27" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3969,1104 +3444,1130 @@
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="N27:P27"/>
   </mergeCells>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:K39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="2.63636363636364" customWidth="1"/>
-    <col min="2" max="2" width="13.6363636363636" customWidth="1"/>
-    <col min="3" max="3" width="15.6363636363636" customWidth="1"/>
-    <col min="4" max="4" width="18.6363636363636" customWidth="1"/>
-    <col min="5" max="5" width="24.6363636363636" customWidth="1"/>
-    <col min="6" max="6" width="72.6363636363636" customWidth="1"/>
-    <col min="7" max="9" width="8.63636363636364" customWidth="1"/>
-    <col min="10" max="10" width="20.6363636363636" customWidth="1"/>
-    <col min="11" max="11" width="14.6363636363636" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" customWidth="1"/>
+    <col min="5" max="5" width="24.6640625" customWidth="1"/>
+    <col min="6" max="6" width="72.6640625" customWidth="1"/>
+    <col min="7" max="9" width="8.6640625" customWidth="1"/>
+    <col min="10" max="10" width="20.6640625" customWidth="1"/>
+    <col min="11" max="11" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="2:11">
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="2:11" ht="21" customHeight="1">
+      <c r="B1" s="32" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="2" ht="20.4" customHeight="1" spans="2:11">
-      <c r="B2" s="2" t="s">
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+    </row>
+    <row r="2" spans="2:11" ht="20.399999999999999" customHeight="1">
+      <c r="B2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="4" t="s">
+      <c r="D2" s="35"/>
+      <c r="E2" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="9"/>
-    </row>
-    <row r="3" ht="15.65" customHeight="1" spans="2:11">
-      <c r="B3" s="10" t="s">
+      <c r="G2" s="37"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="5"/>
+    </row>
+    <row r="3" spans="2:11" ht="15.6" customHeight="1">
+      <c r="B3" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="6" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="4" ht="15.65" customHeight="1" spans="2:11">
-      <c r="B4" s="9"/>
-      <c r="C4" s="10" t="s">
+    <row r="4" spans="2:11" ht="15.6" customHeight="1">
+      <c r="B4" s="5"/>
+      <c r="C4" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-    </row>
-    <row r="5" ht="65" customHeight="1" spans="2:11">
-      <c r="B5" s="12" t="s">
+      <c r="F4" s="5"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+    </row>
+    <row r="5" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B5" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="G5" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H5" s="16" t="s">
+      <c r="G5" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H5" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="I5" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="J5" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1" spans="2:11">
-      <c r="B6" s="12" t="s">
+      <c r="J5" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B6" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="G6" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H6" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I6" s="16" t="s">
+      <c r="G6" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I6" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="J6" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="K6" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1" spans="2:11">
-      <c r="B7" s="12" t="s">
+      <c r="J6" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B7" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="G7" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H7" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I7" s="16" t="s">
+      <c r="G7" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I7" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="J7" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1" spans="2:11">
-      <c r="B8" s="12" t="s">
+      <c r="J7" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B8" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="G8" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H8" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I8" s="16" t="s">
+      <c r="G8" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I8" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="J8" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1" spans="2:11">
-      <c r="B9" s="12" t="s">
+      <c r="J8" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B9" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="G9" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I9" s="16" t="s">
+      <c r="G9" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I9" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="J9" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K9" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1" spans="2:11">
-      <c r="B10" s="12" t="s">
+      <c r="K9" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B10" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G10" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I10" s="16" t="s">
+      <c r="G10" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I10" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="J10" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="K10" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1" spans="2:11">
-      <c r="B11" s="12" t="s">
+      <c r="J10" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B11" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="G11" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H11" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I11" s="16" t="s">
+      <c r="G11" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I11" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="J11" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1" spans="2:11">
-      <c r="B12" s="12" t="s">
+      <c r="J11" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B12" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="G12" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I12" s="16" t="s">
+      <c r="G12" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I12" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="J12" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1" spans="2:11">
-      <c r="B13" s="12" t="s">
+      <c r="J12" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B13" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="G13" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H13" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I13" s="16" t="s">
+      <c r="G13" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I13" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="J13" s="13" t="s">
+      <c r="J13" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="K13" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1" spans="2:11">
-      <c r="B14" s="12" t="s">
+      <c r="K13" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B14" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="G14" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H14" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I14" s="16" t="s">
+      <c r="G14" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I14" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="J14" s="13" t="s">
+      <c r="J14" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="K14" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1" spans="2:11">
-      <c r="B15" s="12" t="s">
+      <c r="K14" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B15" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="G15" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H15" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I15" s="16" t="s">
+      <c r="G15" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I15" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="J15" s="13" t="s">
+      <c r="J15" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K15" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1" spans="2:11">
-      <c r="B16" s="12" t="s">
+      <c r="K15" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B16" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="G16" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H16" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I16" s="16" t="s">
+      <c r="G16" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I16" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="J16" s="13" t="s">
+      <c r="J16" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K16" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1" spans="2:11">
-      <c r="B17" s="12" t="s">
+      <c r="K16" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B17" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="G17" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H17" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I17" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="J17" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="K17" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1" spans="2:11">
-      <c r="B18" s="12" t="s">
+      <c r="G17" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B18" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="G18" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H18" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I18" s="16" t="s">
+      <c r="G18" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I18" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="J18" s="13" t="s">
+      <c r="J18" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K18" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1" spans="2:11">
-      <c r="B19" s="12" t="s">
+      <c r="K18" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B19" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="G19" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H19" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I19" s="16" t="s">
+      <c r="G19" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I19" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="J19" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="K19" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1" spans="2:11">
-      <c r="B20" s="12" t="s">
+      <c r="J19" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B20" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="G20" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H20" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I20" s="16" t="s">
+      <c r="G20" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I20" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="J20" s="13" t="s">
+      <c r="J20" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="K20" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1" spans="2:11">
-      <c r="B21" s="12" t="s">
+      <c r="K20" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B21" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="G21" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H21" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I21" s="16" t="s">
+      <c r="G21" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I21" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="J21" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="K21" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1" spans="2:11">
-      <c r="B22" s="12" t="s">
+      <c r="J21" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B22" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="E22" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F22" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="G22" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H22" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I22" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="J22" s="13" t="s">
+      <c r="G22" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="J22" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K22" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1" spans="2:11">
-      <c r="B23" s="12" t="s">
+      <c r="K22" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B23" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E23" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="F23" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="G23" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H23" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I23" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="J23" s="13" t="s">
+      <c r="G23" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="J23" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K23" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1" spans="2:11">
-      <c r="B24" s="12" t="s">
+      <c r="K23" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B24" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D24" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="E24" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="F24" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="G24" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H24" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I24" s="16" t="s">
+      <c r="G24" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I24" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="J24" s="13" t="s">
+      <c r="J24" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K24" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1" spans="2:11">
-      <c r="B25" s="12" t="s">
+      <c r="K24" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B25" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="E25" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="F25" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="G25" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H25" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I25" s="16" t="s">
+      <c r="G25" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I25" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="J25" s="13" t="s">
+      <c r="J25" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K25" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1" spans="2:11">
-      <c r="B26" s="12" t="s">
+      <c r="K25" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B26" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D26" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="E26" s="13" t="s">
+      <c r="E26" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F26" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="G26" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H26" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I26" s="16" t="s">
+      <c r="G26" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I26" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="J26" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="K26" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1" spans="2:11">
-      <c r="B27" s="12" t="s">
+      <c r="J26" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B27" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="E27" s="13" t="s">
+      <c r="E27" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="G27" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H27" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I27" s="16" t="s">
+      <c r="G27" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I27" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="J27" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="K27" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1" spans="2:11">
-      <c r="B28" s="12" t="s">
+      <c r="J27" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B28" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D28" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="E28" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="F28" s="14" t="s">
+      <c r="F28" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="G28" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H28" s="16" t="s">
+      <c r="G28" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H28" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="I28" s="17" t="s">
+      <c r="I28" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="J28" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="K28" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1" spans="2:11">
-      <c r="B29" s="12" t="s">
+      <c r="J28" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B29" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="E29" s="13" t="s">
+      <c r="E29" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="G29" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H29" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I29" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="J29" s="13" t="s">
+      <c r="G29" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="J29" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K29" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1" spans="2:11">
-      <c r="B30" s="12" t="s">
+      <c r="K29" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B30" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="D30" s="13" t="s">
+      <c r="D30" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="E30" s="13" t="s">
+      <c r="E30" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="F30" s="14" t="s">
+      <c r="F30" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="G30" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H30" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I30" s="16" t="s">
+      <c r="G30" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I30" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="J30" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1" spans="2:11">
-      <c r="B31" s="12" t="s">
+      <c r="J30" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B31" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="E31" s="13" t="s">
+      <c r="E31" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="F31" s="14" t="s">
+      <c r="F31" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="G31" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H31" s="16" t="s">
+      <c r="G31" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H31" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="I31" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="J31" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1" spans="2:11">
-      <c r="B32" s="12" t="s">
+      <c r="I31" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B32" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D32" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="E32" s="13" t="s">
+      <c r="E32" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F32" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="G32" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H32" s="16" t="s">
+      <c r="G32" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H32" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="I32" s="16" t="s">
+      <c r="I32" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="J32" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="K32" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1" spans="2:11">
-      <c r="B33" s="12" t="s">
+      <c r="J32" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B33" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="E33" s="13" t="s">
+      <c r="E33" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="F33" s="14" t="s">
+      <c r="F33" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="G33" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H33" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I33" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="J33" s="13" t="s">
+      <c r="G33" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="J33" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K33" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1" spans="2:11">
-      <c r="B34" s="12" t="s">
+      <c r="K33" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B34" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="E34" s="13" t="s">
+      <c r="E34" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="F34" s="14" t="s">
+      <c r="F34" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="G34" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H34" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I34" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="J34" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="K34" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1" spans="2:11">
-      <c r="B35" s="12" t="s">
+      <c r="G34" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" ht="64.95" customHeight="1">
+      <c r="B35" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="E35" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="F35" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="G35" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="H35" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I35" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="J35" s="13" t="s">
+      <c r="G35" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="J35" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K35" s="13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1" spans="2:11">
-      <c r="B38" s="18" t="s">
+      <c r="K35" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" ht="30" customHeight="1">
+      <c r="B38" s="38" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="39" ht="30" customHeight="1" spans="2:11">
-      <c r="B39" s="18" t="s">
+      <c r="C38" s="33"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="33"/>
+      <c r="H38" s="33"/>
+      <c r="I38" s="33"/>
+      <c r="J38" s="33"/>
+      <c r="K38" s="33"/>
+    </row>
+    <row r="39" spans="2:11" ht="30" customHeight="1">
+      <c r="B39" s="38" t="s">
         <v>228</v>
       </c>
+      <c r="C39" s="33"/>
+      <c r="D39" s="33"/>
+      <c r="E39" s="33"/>
+      <c r="F39" s="33"/>
+      <c r="G39" s="33"/>
+      <c r="H39" s="33"/>
+      <c r="I39" s="33"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -5076,60 +4577,56 @@
     <mergeCell ref="B38:K38"/>
     <mergeCell ref="B39:K39"/>
   </mergeCells>
+  <phoneticPr fontId="20" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="无效状态" error="状态必须为 ○、△、× 或 N/A" promptTitle="需求状态" prompt="请选择 PD、COD 或 UT 状态" sqref="G5:I29">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="无效状态" error="状态必须为 ○、△、× 或 N/A" promptTitle="需求状态" prompt="请选择 PD、COD 或 UT 状态" sqref="G5:I29" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"○,△,×,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>